--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.32416069509536</v>
+        <v>3.140176112952997</v>
       </c>
       <c r="D2" t="n">
-        <v>12.96757158115621</v>
+        <v>2.107230381937884</v>
       </c>
       <c r="E2" t="n">
-        <v>11.82028145372887</v>
+        <v>1.92079573623094</v>
       </c>
       <c r="F2" t="n">
-        <v>5.588840871781498</v>
+        <v>0.9081866416644933</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.49513049321847</v>
+        <v>4.792958705148001</v>
       </c>
       <c r="D3" t="n">
-        <v>19.49956437561082</v>
+        <v>3.168679211036758</v>
       </c>
       <c r="E3" t="n">
-        <v>11.82028145372887</v>
+        <v>1.92079573623094</v>
       </c>
       <c r="F3" t="n">
-        <v>5.588840871781498</v>
+        <v>0.9081866416644933</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.88621415577597</v>
+        <v>7.781509800313596</v>
       </c>
       <c r="D4" t="n">
-        <v>26.65268228360754</v>
+        <v>4.331060871086225</v>
       </c>
       <c r="E4" t="n">
-        <v>11.82028145372887</v>
+        <v>1.92079573623094</v>
       </c>
       <c r="F4" t="n">
-        <v>5.588840871781498</v>
+        <v>0.9081866416644933</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
